--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1070,7 +1070,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/event-status</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFRadiologyProcedureStatus</t>
   </si>
   <si>
     <t xml:space="preserve">us-core-7
@@ -617,7 +617,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>1506: source value from EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (#70.03-3 &gt; 72-.01)</t>
+    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (#70.03-3 &gt; 72-.01)</t>
   </si>
   <si>
     <t>Dim.RadiologyExamStatus.RadiologyExamStatus</t>
@@ -1782,7 +1782,7 @@
     <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="123.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="140.26953125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="58.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -953,15 +953,7 @@
     <t>1512: source value from REGISTERED EXAMS - EXAM DATE (#70.02-.01)</t>
   </si>
   <si>
-    <t>Rad.RadiologyExam.ExamDateTime
-Rad.RadiologyExamActivityLog.ExamDateTime
-Rad.RadiologyExamContrastMedia.ExamDateTime
-Rad.RadiologyExamCPTModifier.ExamDateTime
-Rad.RadiologyExamMedication.ExamDateTime
-Rad.RadiologyExamSecondaryDiagnosticCode.ExamDateTime
-Rad.RadiologyExamStatusList.ExamDateTime
-Rad.RadiologyExamTechnologist.ExamDateTime
-Rad.RadiologyRegisteredExam.ExamDateTime</t>
+    <t>Rad.RadiologyExam.ExamDateTime,Rad.RadiologyExamActivityLog.ExamDateTime,Rad.RadiologyExamContrastMedia.ExamDateTime,Rad.RadiologyExamCPTModifier.ExamDateTime,Rad.RadiologyExamMedication.ExamDateTime,Rad.RadiologyExamSecondaryDiagnosticCode.ExamDateTime,Rad.RadiologyExamStatusList.ExamDateTime,Rad.RadiologyExamTechnologist.ExamDateTime,Rad.RadiologyRegisteredExam.ExamDateTime</t>
   </si>
   <si>
     <t>Procedure.recorder</t>
@@ -1783,7 +1775,7 @@
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="140.26953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="58.35546875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -608,6 +608,12 @@
 </t>
   </si>
   <si>
+    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (#70.03-3 &gt; 72-.01)</t>
+  </si>
+  <si>
+    <t>Dim.RadiologyExamStatus.RadiologyExamStatus</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -615,12 +621,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (#70.03-3 &gt; 72-.01)</t>
-  </si>
-  <si>
-    <t>Dim.RadiologyExamStatus.RadiologyExamStatus</t>
   </si>
   <si>
     <t>Procedure.statusReason</t>
@@ -742,16 +742,16 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1507: source value from EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (#70.03-3.5 &gt; 75.2-.01)</t>
+  </si>
+  <si>
+    <t>Dim.RadiologyHoldCancelReason.RadiologyHoldCancelReason</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>1507: source value from EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (#70.03-3.5 &gt; 75.2-.01)</t>
-  </si>
-  <si>
-    <t>Dim.RadiologyHoldCancelReason.RadiologyHoldCancelReason</t>
   </si>
   <si>
     <t>Procedure.category</t>
@@ -862,6 +862,9 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
+    <t>1510: reference from RAD/NUC MED PATIENT - NAME (#70-.01)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -872,9 +875,6 @@
   </si>
   <si>
     <t>PID-3</t>
-  </si>
-  <si>
-    <t>1510: reference from RAD/NUC MED PATIENT - NAME (#70-.01)</t>
   </si>
   <si>
     <t>Procedure.encounter</t>
@@ -893,6 +893,9 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
+    <t>1511: reference from EXAMINATIONS - VISIT (#70.03-27)</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -903,9 +906,6 @@
   </si>
   <si>
     <t>PV1-19</t>
-  </si>
-  <si>
-    <t>1511: reference from EXAMINATIONS - VISIT (#70.03-27)</t>
   </si>
   <si>
     <t>Procedure.performed[x]</t>
@@ -1075,6 +1075,9 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
+    <t>1513: reference from EXAMINATIONS - PRIMARY INTERPRETING STAFF (#70.03-15)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1085,9 +1088,6 @@
   </si>
   <si>
     <t>ORC-19/PRT-5</t>
-  </si>
-  <si>
-    <t>1513: reference from EXAMINATIONS - PRIMARY INTERPRETING STAFF (#70.03-15)</t>
   </si>
   <si>
     <t>Procedure.performer.onBehalfOf</t>
@@ -1125,13 +1125,13 @@
     <t>Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
+    <t>1514: reference from REGISTERED EXAMS - IMAGING LOCATION &gt; IMAGING LOCATIONS - LOCATION (#70.02-4 &gt; 79.1-.01)</t>
+  </si>
+  <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>
   </si>
   <si>
     <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>1514: reference from REGISTERED EXAMS - IMAGING LOCATION &gt; IMAGING LOCATIONS - LOCATION (#70.02-4 &gt; 79.1-.01)</t>
   </si>
   <si>
     <t>Procedure.reasonCode</t>
@@ -1770,12 +1770,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="140.26953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="140.26953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="105.16015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2008,16 +2008,16 @@
         <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>79</v>
@@ -2609,13 +2609,13 @@
         <v>79</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>79</v>
@@ -2729,13 +2729,13 @@
         <v>79</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>79</v>
@@ -2849,13 +2849,13 @@
         <v>79</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>79</v>
@@ -2971,13 +2971,13 @@
         <v>79</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>79</v>
@@ -3090,22 +3090,22 @@
         <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3208,16 +3208,16 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3328,16 +3328,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3446,16 +3446,16 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3566,16 +3566,16 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3693,13 +3693,13 @@
         <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>193</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -3804,16 +3804,16 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3925,13 +3925,13 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -4045,13 +4045,13 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4167,19 +4167,19 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4286,19 +4286,19 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>235</v>
@@ -4407,16 +4407,16 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -4525,13 +4525,13 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4645,13 +4645,13 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4767,19 +4767,19 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4886,22 +4886,22 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>248</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5006,22 +5006,22 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5127,13 +5127,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5247,13 +5247,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5366,22 +5366,22 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5491,19 +5491,19 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5609,19 +5609,19 @@
         <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5729,19 +5729,19 @@
         <v>281</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -5844,22 +5844,22 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -5966,22 +5966,22 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6087,16 +6087,16 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6205,16 +6205,16 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6320,16 +6320,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6441,13 +6441,13 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6561,13 +6561,13 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6683,13 +6683,13 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6800,22 +6800,22 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -6923,19 +6923,19 @@
         <v>339</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7043,13 +7043,13 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7160,16 +7160,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>357</v>
@@ -7280,19 +7280,19 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -7400,19 +7400,19 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -7523,19 +7523,19 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -7643,13 +7643,13 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7763,13 +7763,13 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7883,13 +7883,13 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8003,13 +8003,13 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8121,13 +8121,13 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8236,22 +8236,22 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -8357,13 +8357,13 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8475,13 +8475,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8595,13 +8595,13 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8717,13 +8717,13 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8835,13 +8835,13 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8953,13 +8953,13 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9075,13 +9075,13 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9195,13 +9195,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file EXAMINATIONS (#70.03) to us-core-procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file EXAMINATIONS (70.03) to us-core-procedure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -608,7 +608,7 @@
 </t>
   </si>
   <si>
-    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (#70.03-3 &gt; 72-.01)</t>
+    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (70.03-3 &gt; 72-.01)</t>
   </si>
   <si>
     <t>Dim.RadiologyExamStatus.RadiologyExamStatus</t>
@@ -742,7 +742,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1507: source value from EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (#70.03-3.5 &gt; 75.2-.01)</t>
+    <t>1507: source value from EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (70.03-3.5 &gt; 75.2-.01)</t>
   </si>
   <si>
     <t>Dim.RadiologyHoldCancelReason.RadiologyHoldCancelReason</t>
@@ -787,7 +787,7 @@
     <t>Procedure.category.text</t>
   </si>
   <si>
-    <t>1508: source value from REGISTERED EXAMS - TYPE OF IMAGING &gt; IMAGING TYPE - TYPE OF IMAGING (#70.02-2 &gt; 79.2-.01)</t>
+    <t>1508: source value from REGISTERED EXAMS - TYPE OF IMAGING &gt; IMAGING TYPE - TYPE OF IMAGING (70.02-2 &gt; 79.2-.01)</t>
   </si>
   <si>
     <t>Dim.ImagingType.ImagingType</t>
@@ -839,7 +839,7 @@
     <t>Procedure.code.coding</t>
   </si>
   <si>
-    <t>1509: source value from EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (#70.03-2 &gt; 71-9 &gt; 81-)</t>
+    <t>1509: source value from EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (70.03-2 &gt; 71-9 &gt; 81-)</t>
   </si>
   <si>
     <t>Procedure.code.text</t>
@@ -862,7 +862,7 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
-    <t>1510: reference from RAD/NUC MED PATIENT - NAME (#70-.01)</t>
+    <t>1510: reference from RAD/NUC MED PATIENT - NAME (70-.01)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -893,7 +893,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>1511: reference from EXAMINATIONS - VISIT (#70.03-27)</t>
+    <t>1511: reference from EXAMINATIONS - VISIT (70.03-27)</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -950,7 +950,7 @@
 </t>
   </si>
   <si>
-    <t>1512: source value from REGISTERED EXAMS - EXAM DATE (#70.02-.01)</t>
+    <t>1512: source value from REGISTERED EXAMS - EXAM DATE (70.02-.01)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.ExamDateTime,Rad.RadiologyExamActivityLog.ExamDateTime,Rad.RadiologyExamContrastMedia.ExamDateTime,Rad.RadiologyExamCPTModifier.ExamDateTime,Rad.RadiologyExamMedication.ExamDateTime,Rad.RadiologyExamSecondaryDiagnosticCode.ExamDateTime,Rad.RadiologyExamStatusList.ExamDateTime,Rad.RadiologyExamTechnologist.ExamDateTime,Rad.RadiologyRegisteredExam.ExamDateTime</t>
@@ -1075,7 +1075,7 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
-    <t>1513: reference from EXAMINATIONS - PRIMARY INTERPRETING STAFF (#70.03-15)</t>
+    <t>1513: reference from EXAMINATIONS - PRIMARY INTERPRETING STAFF (70.03-15)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1125,7 +1125,7 @@
     <t>Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
-    <t>1514: reference from REGISTERED EXAMS - IMAGING LOCATION &gt; IMAGING LOCATIONS - LOCATION (#70.02-4 &gt; 79.1-.01)</t>
+    <t>1514: reference from REGISTERED EXAMS - IMAGING LOCATION &gt; IMAGING LOCATIONS - LOCATION (70.02-4 &gt; 79.1-.01)</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>
@@ -1770,7 +1770,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="140.26953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="138.734375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2389" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2389" uniqueCount="455">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -611,7 +611,8 @@
     <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (70.03-3 &gt; 72-.01)</t>
   </si>
   <si>
-    <t>Dim.RadiologyExamStatus.RadiologyExamStatus</t>
+    <t>Rad.RadiologyExam.RadiologyExamStatusIEN
+Dim.RadiologyExamStatus.RadiologyExamStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -745,7 +746,8 @@
     <t>1507: source value from EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (70.03-3.5 &gt; 75.2-.01)</t>
   </si>
   <si>
-    <t>Dim.RadiologyHoldCancelReason.RadiologyHoldCancelReason</t>
+    <t>Rad.RadiologyExam.RadiologyHoldCancelReasonIEN
+Dim.RadiologyHoldCancelReason.RadiologyHoldCancelReason</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -790,7 +792,8 @@
     <t>1508: source value from REGISTERED EXAMS - TYPE OF IMAGING &gt; IMAGING TYPE - TYPE OF IMAGING (70.02-2 &gt; 79.2-.01)</t>
   </si>
   <si>
-    <t>Dim.ImagingType.ImagingType</t>
+    <t>Rad.RadiologyRegisteredExam.ImagingTypeIEN
+Dim.ImagingType.ImagingType</t>
   </si>
   <si>
     <t>Procedure.code</t>
@@ -842,6 +845,9 @@
     <t>1509: source value from EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (70.03-2 &gt; 71-9 &gt; 81-)</t>
   </si>
   <si>
+    <t>Rad.RadiologyExam.RadiologyProcedureIEN</t>
+  </si>
+  <si>
     <t>Procedure.code.text</t>
   </si>
   <si>
@@ -865,6 +871,9 @@
     <t>1510: reference from RAD/NUC MED PATIENT - NAME (70-.01)</t>
   </si>
   <si>
+    <t>Patient.RadiologyPatient.PatientIEN,Rad.RadiologyExam.PatientIEN,Rad.RadiologyExamActivityLog.PatientIEN,Rad.RadiologyExamContrastMedia.PatientIEN,Rad.RadiologyExamCPTModifier.PatientIEN,Rad.RadiologyExamMedication.PatientIEN,Rad.RadiologyExamSecondaryDiagnosticCode.PatientIEN,Rad.RadiologyExamStatusList.PatientIEN,Rad.RadiologyFilmRegistry.PatientIEN,Rad.RadiologyRegisteredExam.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -896,6 +905,9 @@
     <t>1511: reference from EXAMINATIONS - VISIT (70.03-27)</t>
   </si>
   <si>
+    <t>Rad.RadiologyExam.VisitIEN</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -1078,6 +1090,9 @@
     <t>1513: reference from EXAMINATIONS - PRIMARY INTERPRETING STAFF (70.03-15)</t>
   </si>
   <si>
+    <t>Rad.RadiologyExam.PrimaryInterpretingStaffIEN</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1126,6 +1141,10 @@
   </si>
   <si>
     <t>1514: reference from REGISTERED EXAMS - IMAGING LOCATION &gt; IMAGING LOCATIONS - LOCATION (70.02-4 &gt; 79.1-.01)</t>
+  </si>
+  <si>
+    <t>Rad.RadiologyRegisteredExam.RadiologyLocationIEN
+Dim.RadiologyLocation.LocationIEN</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>
@@ -5369,7 +5388,7 @@
         <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5386,10 +5405,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5508,14 +5527,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5534,13 +5553,13 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5591,7 +5610,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>89</v>
@@ -5606,30 +5625,30 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5652,16 +5671,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5711,7 +5730,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5726,30 +5745,30 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5772,16 +5791,16 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5819,7 +5838,7 @@
         <v>79</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -5829,7 +5848,7 @@
         <v>215</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5850,27 +5869,27 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -5892,16 +5911,16 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5951,7 +5970,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5966,30 +5985,30 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6012,13 +6031,13 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6069,7 +6088,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6093,10 +6112,10 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6104,10 +6123,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6130,13 +6149,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6187,7 +6206,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6211,10 +6230,10 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -6222,10 +6241,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6248,13 +6267,13 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6305,7 +6324,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6326,10 +6345,10 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6340,10 +6359,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6458,10 +6477,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6578,14 +6597,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6607,10 +6626,10 @@
         <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>138</v>
@@ -6665,7 +6684,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6700,10 +6719,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6729,14 +6748,14 @@
         <v>196</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6764,10 +6783,10 @@
         <v>200</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6785,7 +6804,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6806,24 +6825,24 @@
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6846,17 +6865,17 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6905,7 +6924,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>89</v>
@@ -6920,30 +6939,30 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6966,17 +6985,17 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7025,7 +7044,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7049,7 +7068,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7060,10 +7079,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7086,17 +7105,17 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7145,7 +7164,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7160,19 +7179,19 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7180,10 +7199,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7209,13 +7228,13 @@
         <v>196</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7244,28 +7263,28 @@
         <v>200</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Z46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7286,13 +7305,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -7300,10 +7319,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7326,16 +7345,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7385,7 +7404,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7406,13 +7425,13 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -7420,10 +7439,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7449,13 +7468,13 @@
         <v>196</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7484,28 +7503,28 @@
         <v>200</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Z48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7529,21 +7548,21 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7569,13 +7588,13 @@
         <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7604,28 +7623,28 @@
         <v>200</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Z49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7649,7 +7668,7 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7660,10 +7679,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7686,16 +7705,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7745,7 +7764,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7769,7 +7788,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7780,10 +7799,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7809,13 +7828,13 @@
         <v>196</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7844,28 +7863,28 @@
         <v>200</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Z51" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7889,7 +7908,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7900,10 +7919,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7926,17 +7945,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7985,7 +8004,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8009,7 +8028,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8020,10 +8039,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8049,10 +8068,10 @@
         <v>196</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8082,10 +8101,10 @@
         <v>200</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8103,7 +8122,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8127,7 +8146,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8138,10 +8157,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8164,13 +8183,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8221,7 +8240,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8242,24 +8261,24 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8282,13 +8301,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8339,7 +8358,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8363,7 +8382,7 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8374,10 +8393,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8492,10 +8511,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8612,14 +8631,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8641,10 +8660,10 @@
         <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>138</v>
@@ -8699,7 +8718,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8734,10 +8753,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8763,10 +8782,10 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8796,10 +8815,10 @@
         <v>113</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -8817,7 +8836,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8841,7 +8860,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8852,10 +8871,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8878,13 +8897,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8935,7 +8954,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>89</v>
@@ -8959,7 +8978,7 @@
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -8970,10 +8989,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8996,19 +9015,19 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9057,7 +9076,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9081,7 +9100,7 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9092,10 +9111,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9121,13 +9140,13 @@
         <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9156,10 +9175,10 @@
         <v>200</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>79</v>
@@ -9177,7 +9196,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9201,7 +9220,7 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2389" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="499">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -846,6 +846,139 @@
   </si>
   <si>
     <t>Rad.RadiologyExam.RadiologyProcedureIEN</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://www.ama-assn.org/go/cpt</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1509-1: fixed value = http://www.ama-assn.org/go/cpt</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1509-2: source value from EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - CPT CODE (70.03-2 &gt; 71-9 &gt; 81-.01)</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1509-3: source value from EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - SHORT NAME (70.03-2 &gt; 71-9 &gt; 81-2)</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
   </si>
   <si>
     <t>Procedure.code.text</t>
@@ -1751,7 +1884,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.296875" customWidth="true" bestFit="true"/>
@@ -5428,23 +5561,19 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>206</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5492,7 +5621,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5504,7 +5633,7 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
@@ -5516,13 +5645,13 @@
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5534,34 +5663,36 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>268</v>
+        <v>134</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5598,57 +5729,57 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5671,18 +5802,20 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>279</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5691,7 +5824,7 @@
         <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>79</v>
@@ -5730,7 +5863,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5745,30 +5878,30 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5782,7 +5915,7 @@
         <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -5791,16 +5924,16 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>290</v>
+        <v>206</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5838,17 +5971,19 @@
         <v>79</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AC34" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5857,7 +5992,7 @@
         <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>101</v>
@@ -5869,28 +6004,26 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5911,18 +6044,18 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>301</v>
+        <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5979,36 +6112,36 @@
         <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6022,7 +6155,7 @@
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
@@ -6031,16 +6164,18 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>305</v>
+        <v>206</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6088,7 +6223,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6103,30 +6238,30 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6149,16 +6284,20 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6206,7 +6345,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6230,21 +6369,21 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6255,7 +6394,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6267,16 +6406,20 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>317</v>
+        <v>227</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6324,13 +6467,13 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>231</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
@@ -6345,53 +6488,53 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>320</v>
+        <v>234</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>313</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>207</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6442,10 +6585,10 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>209</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>89</v>
@@ -6454,25 +6597,25 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>210</v>
+        <v>319</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -6484,35 +6627,35 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>135</v>
+        <v>323</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>136</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>325</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>138</v>
+        <v>326</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6562,81 +6705,79 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>79</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>135</v>
+        <v>334</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6672,31 +6813,29 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
@@ -6705,26 +6844,28 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>132</v>
+        <v>340</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6736,7 +6877,7 @@
         <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>79</v>
@@ -6745,18 +6886,18 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>196</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6780,31 +6921,31 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="Z42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6813,36 +6954,36 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6850,13 +6991,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
@@ -6865,18 +7006,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>341</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6924,10 +7063,10 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
@@ -6939,30 +7078,30 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>343</v>
+        <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>344</v>
+        <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6982,21 +7121,19 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>349</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>352</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7044,7 +7181,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7068,10 +7205,10 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>358</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7079,10 +7216,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7093,10 +7230,10 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
@@ -7105,18 +7242,16 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>358</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -7164,13 +7299,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7179,19 +7314,19 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7199,10 +7334,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7213,7 +7348,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7222,20 +7357,18 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>364</v>
+        <v>207</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7260,13 +7393,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7284,19 +7417,19 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>209</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7305,13 +7438,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>370</v>
+        <v>210</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -7319,14 +7452,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7342,19 +7475,19 @@
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>373</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>136</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>212</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>376</v>
+        <v>138</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7404,7 +7537,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>216</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7416,7 +7549,7 @@
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7425,13 +7558,13 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>370</v>
+        <v>210</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -7439,14 +7572,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7459,24 +7592,26 @@
         <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7500,13 +7635,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7524,7 +7659,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7536,7 +7671,7 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7548,21 +7683,21 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>384</v>
+        <v>132</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>385</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7588,15 +7723,15 @@
         <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7623,10 +7758,10 @@
         <v>200</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7644,7 +7779,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7665,24 +7800,24 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>79</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7690,33 +7825,33 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7764,13 +7899,13 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
@@ -7779,30 +7914,30 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7813,7 +7948,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7825,18 +7960,18 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>196</v>
+        <v>393</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7860,13 +7995,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7884,13 +8019,13 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
@@ -7908,7 +8043,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7919,10 +8054,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7933,29 +8068,29 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8004,13 +8139,13 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
@@ -8019,10 +8154,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8031,7 +8166,7 @@
         <v>405</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>79</v>
+        <v>406</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8039,10 +8174,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8062,18 +8197,20 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8101,10 +8238,10 @@
         <v>200</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8122,7 +8259,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8143,13 +8280,13 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>79</v>
@@ -8157,10 +8294,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8180,18 +8317,20 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8240,7 +8379,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8264,21 +8403,21 @@
         <v>421</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>423</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8298,18 +8437,20 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>316</v>
+        <v>196</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8334,13 +8475,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>79</v>
+        <v>427</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8358,7 +8499,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8382,21 +8523,21 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8416,18 +8557,20 @@
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>207</v>
+        <v>431</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8452,13 +8595,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>79</v>
+        <v>434</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8476,7 +8619,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>209</v>
+        <v>430</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8488,7 +8631,7 @@
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
@@ -8500,7 +8643,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>210</v>
+        <v>436</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8511,14 +8654,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8537,16 +8680,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>438</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>136</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>212</v>
+        <v>440</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>138</v>
+        <v>441</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8596,7 +8739,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>216</v>
+        <v>437</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8608,7 +8751,7 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
@@ -8620,7 +8763,7 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>210</v>
+        <v>442</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8631,14 +8774,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8651,26 +8794,24 @@
         <v>79</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>325</v>
+        <v>444</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>326</v>
+        <v>445</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8694,13 +8835,13 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>79</v>
+        <v>448</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8718,7 +8859,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>327</v>
+        <v>443</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8730,7 +8871,7 @@
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -8742,7 +8883,7 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>132</v>
+        <v>449</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8753,10 +8894,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8767,7 +8908,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -8779,16 +8920,18 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>196</v>
+        <v>451</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8812,13 +8955,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>435</v>
+        <v>79</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -8836,13 +8979,13 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
@@ -8860,7 +9003,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8871,10 +9014,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8882,10 +9025,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -8897,13 +9040,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>438</v>
+        <v>196</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8930,13 +9073,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>79</v>
+        <v>459</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -8954,13 +9097,13 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
@@ -8978,7 +9121,7 @@
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -8989,10 +9132,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9015,20 +9158,16 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9076,7 +9215,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9097,24 +9236,24 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>79</v>
+        <v>467</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9137,17 +9276,15 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>196</v>
+        <v>360</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9172,13 +9309,13 @@
         <v>79</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>452</v>
+        <v>79</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>453</v>
+        <v>79</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>79</v>
@@ -9196,7 +9333,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9220,17 +9357,855 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP62">
+  <autoFilter ref="A1:AP69">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9240,7 +10215,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="496">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file EXAMINATIONS (70.03) to us-core-procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file REGISTRED EXAMS (70.02) to us-core-procedure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -608,11 +608,7 @@
 </t>
   </si>
   <si>
-    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (70.03-3 &gt; 72-.01)</t>
-  </si>
-  <si>
-    <t>Rad.RadiologyExam.RadiologyExamStatusIEN
-Dim.RadiologyExamStatus.RadiologyExamStatus</t>
+    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (70.02-50 &gt; 70.03-3 &gt; 72-.01)</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -743,11 +739,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1507: source value from EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (70.03-3.5 &gt; 75.2-.01)</t>
-  </si>
-  <si>
-    <t>Rad.RadiologyExam.RadiologyHoldCancelReasonIEN
-Dim.RadiologyHoldCancelReason.RadiologyHoldCancelReason</t>
+    <t>1507: source value from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (70.02-50 &gt; 70.03-3.5 &gt; 75.2-.01)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -842,10 +834,7 @@
     <t>Procedure.code.coding</t>
   </si>
   <si>
-    <t>1509: source value from EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (70.03-2 &gt; 71-9 &gt; 81-)</t>
-  </si>
-  <si>
-    <t>Rad.RadiologyExam.RadiologyProcedureIEN</t>
+    <t>1509: source value from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-)</t>
   </si>
   <si>
     <t>Procedure.code.coding.id</t>
@@ -920,7 +909,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1509-2: source value from EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - CPT CODE (70.03-2 &gt; 71-9 &gt; 81-.01)</t>
+    <t>1509-2: source value from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - CPT CODE (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-.01)</t>
   </si>
   <si>
     <t>./code</t>
@@ -944,7 +933,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1509-3: source value from EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - SHORT NAME (70.03-2 &gt; 71-9 &gt; 81-2)</t>
+    <t>1509-3: source value from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - SHORT NAME (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-2)</t>
   </si>
   <si>
     <t>CV.displayName</t>
@@ -1001,7 +990,7 @@
     <t>The person, animal or group on which the procedure was performed.</t>
   </si>
   <si>
-    <t>1510: reference from RAD/NUC MED PATIENT - NAME (70-.01)</t>
+    <t>1510: reference from RAD/NUC MED PATIENT - NAME (70-.01) case 70-2 &gt; 70.02</t>
   </si>
   <si>
     <t>Patient.RadiologyPatient.PatientIEN,Rad.RadiologyExam.PatientIEN,Rad.RadiologyExamActivityLog.PatientIEN,Rad.RadiologyExamContrastMedia.PatientIEN,Rad.RadiologyExamCPTModifier.PatientIEN,Rad.RadiologyExamMedication.PatientIEN,Rad.RadiologyExamSecondaryDiagnosticCode.PatientIEN,Rad.RadiologyExamStatusList.PatientIEN,Rad.RadiologyFilmRegistry.PatientIEN,Rad.RadiologyRegisteredExam.PatientIEN</t>
@@ -1035,7 +1024,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>1511: reference from EXAMINATIONS - VISIT (70.03-27)</t>
+    <t>1511: reference from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - VISIT (70.02-50 &gt; 70.03-27)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.VisitIEN</t>
@@ -1220,7 +1209,7 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
-    <t>1513: reference from EXAMINATIONS - PRIMARY INTERPRETING STAFF (70.03-15)</t>
+    <t>1513: reference from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PRIMARY INTERPRETING STAFF (70.02-50 &gt; 70.03-15)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.PrimaryInterpretingStaffIEN</t>
@@ -1922,7 +1911,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="138.734375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="185.78125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>
@@ -3839,16 +3828,16 @@
         <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>79</v>
@@ -3856,14 +3845,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3882,16 +3871,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3917,14 +3906,14 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
       </c>
@@ -3941,7 +3930,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3962,10 +3951,10 @@
         <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3976,10 +3965,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4002,13 +3991,13 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4059,7 +4048,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4083,7 +4072,7 @@
         <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -4094,10 +4083,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4126,7 +4115,7 @@
         <v>136</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>138</v>
@@ -4167,19 +4156,19 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AC19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AC19" t="s" s="2">
+      <c r="AD19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AD19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE19" t="s" s="2">
+      <c r="AF19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4203,7 +4192,7 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4214,10 +4203,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4240,19 +4229,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4301,7 +4290,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4325,21 +4314,21 @@
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4362,19 +4351,19 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4423,7 +4412,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4438,30 +4427,30 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4484,13 +4473,13 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4517,13 +4506,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4541,7 +4530,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4565,10 +4554,10 @@
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -4576,10 +4565,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4602,13 +4591,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4659,7 +4648,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4683,7 +4672,7 @@
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4694,10 +4683,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4726,7 +4715,7 @@
         <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>138</v>
@@ -4767,19 +4756,19 @@
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AC24" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AC24" t="s" s="2">
+      <c r="AD24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE24" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AD24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE24" t="s" s="2">
+      <c r="AF24" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4803,7 +4792,7 @@
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4814,10 +4803,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4840,19 +4829,19 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4901,7 +4890,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4925,21 +4914,21 @@
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4962,19 +4951,19 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5023,7 +5012,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5038,34 +5027,34 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5084,17 +5073,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5119,14 +5108,14 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="Y27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5143,7 +5132,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5164,24 +5153,24 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5204,13 +5193,13 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5261,7 +5250,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5285,7 +5274,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5296,10 +5285,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5328,7 +5317,7 @@
         <v>136</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>138</v>
@@ -5369,19 +5358,19 @@
         <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AC29" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AD29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AF29" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5405,7 +5394,7 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5416,10 +5405,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5442,19 +5431,19 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5503,7 +5492,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5518,30 +5507,30 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5564,13 +5553,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5621,7 +5610,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5645,7 +5634,7 @@
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5656,10 +5645,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5688,7 +5677,7 @@
         <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>138</v>
@@ -5729,19 +5718,19 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AC32" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AC32" t="s" s="2">
+      <c r="AD32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE32" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AD32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE32" t="s" s="2">
+      <c r="AF32" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5765,7 +5754,7 @@
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5776,10 +5765,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5805,16 +5794,16 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5824,7 +5813,7 @@
         <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>79</v>
@@ -5863,7 +5852,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5878,7 +5867,7 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>79</v>
@@ -5887,21 +5876,21 @@
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5924,16 +5913,16 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5983,7 +5972,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6007,21 +5996,21 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6047,14 +6036,14 @@
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6103,7 +6092,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6118,30 +6107,30 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6164,17 +6153,17 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6223,7 +6212,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6238,30 +6227,30 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6284,19 +6273,19 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6345,7 +6334,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6369,21 +6358,21 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6406,19 +6395,19 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6467,7 +6456,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6491,25 +6480,25 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6528,13 +6517,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6585,7 +6574,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>89</v>
@@ -6600,30 +6589,30 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6646,16 +6635,16 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6705,7 +6694,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6720,30 +6709,30 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6766,16 +6755,16 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6813,17 +6802,17 @@
         <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6844,27 +6833,27 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>79</v>
@@ -6886,16 +6875,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6945,7 +6934,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6960,30 +6949,30 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7006,13 +6995,13 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7063,7 +7052,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7087,10 +7076,10 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7098,10 +7087,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7124,13 +7113,13 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7181,7 +7170,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7205,10 +7194,10 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7216,10 +7205,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7242,13 +7231,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7299,7 +7288,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7320,10 +7309,10 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7334,10 +7323,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7360,13 +7349,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7417,7 +7406,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7441,7 +7430,7 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7452,10 +7441,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7484,7 +7473,7 @@
         <v>136</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>138</v>
@@ -7537,7 +7526,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7561,7 +7550,7 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7572,14 +7561,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7601,10 +7590,10 @@
         <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>138</v>
@@ -7659,7 +7648,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7694,10 +7683,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7720,17 +7709,17 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7755,13 +7744,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7779,7 +7768,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7800,24 +7789,24 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7840,17 +7829,17 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7899,7 +7888,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -7914,30 +7903,30 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7960,17 +7949,17 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8019,7 +8008,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8043,7 +8032,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8054,10 +8043,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8080,17 +8069,17 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8139,7 +8128,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8154,19 +8143,19 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -8174,10 +8163,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8200,16 +8189,16 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8235,13 +8224,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8259,7 +8248,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8280,13 +8269,13 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>79</v>
@@ -8294,10 +8283,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8320,16 +8309,16 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8379,7 +8368,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8400,13 +8389,13 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>79</v>
@@ -8414,10 +8403,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8440,16 +8429,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8475,13 +8464,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8499,7 +8488,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8523,21 +8512,21 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8560,16 +8549,16 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8595,13 +8584,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8619,7 +8608,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8643,7 +8632,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8654,10 +8643,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8680,16 +8669,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8739,7 +8728,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8763,7 +8752,7 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8774,10 +8763,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8800,16 +8789,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8835,13 +8824,13 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8859,7 +8848,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8883,7 +8872,7 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8894,10 +8883,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8920,17 +8909,17 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -8979,7 +8968,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9003,7 +8992,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -9014,10 +9003,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9040,13 +9029,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9073,13 +9062,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9097,7 +9086,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9121,7 +9110,7 @@
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9132,10 +9121,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9158,13 +9147,13 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9215,7 +9204,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9236,24 +9225,24 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9276,13 +9265,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9333,7 +9322,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9357,7 +9346,7 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9368,10 +9357,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9394,13 +9383,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9451,7 +9440,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9475,7 +9464,7 @@
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9486,10 +9475,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9518,7 +9507,7 @@
         <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>138</v>
@@ -9571,7 +9560,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9595,7 +9584,7 @@
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9606,14 +9595,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9635,10 +9624,10 @@
         <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
@@ -9693,7 +9682,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9728,10 +9717,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9754,13 +9743,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9790,10 +9779,10 @@
         <v>113</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>79</v>
@@ -9811,7 +9800,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9835,7 +9824,7 @@
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -9846,10 +9835,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9872,13 +9861,13 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9929,7 +9918,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>89</v>
@@ -9953,7 +9942,7 @@
         <v>79</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>79</v>
@@ -9964,10 +9953,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9990,19 +9979,19 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -10051,7 +10040,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10075,7 +10064,7 @@
         <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
@@ -10086,10 +10075,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10112,16 +10101,16 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10147,13 +10136,13 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10171,7 +10160,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10195,7 +10184,7 @@
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -980,7 +980,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1196,7 +1196,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file REGISTRED EXAMS (70.02) to us-core-procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file REGISTERED EXAMS (70.02) to us-core-procedure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -608,7 +608,7 @@
 </t>
   </si>
   <si>
-    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (70.02-50 &gt; 70.03-3 &gt; 72-.01)</t>
+    <t>1506: terminologyMaps using VF_RadiologyProcedureStatus on REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (70.02-50 &gt; 70.03-3 &gt; 72-.01)</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -739,7 +739,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1507: source value from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (70.02-50 &gt; 70.03-3.5 &gt; 75.2-.01)</t>
+    <t>1507: source value from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (70.02-50 &gt; 70.03-3.5 &gt; 75.2-.01)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -834,7 +834,7 @@
     <t>Procedure.code.coding</t>
   </si>
   <si>
-    <t>1509: source value from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-)</t>
+    <t>1509: source value from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-)</t>
   </si>
   <si>
     <t>Procedure.code.coding.id</t>
@@ -909,7 +909,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1509-2: source value from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - CPT CODE (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-.01)</t>
+    <t>1509-2: source value from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - CPT CODE (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-.01)</t>
   </si>
   <si>
     <t>./code</t>
@@ -933,7 +933,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1509-3: source value from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - SHORT NAME (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-2)</t>
+    <t>1509-3: source value from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - SHORT NAME (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-2)</t>
   </si>
   <si>
     <t>CV.displayName</t>
@@ -1024,7 +1024,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>1511: reference from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - VISIT (70.02-50 &gt; 70.03-27)</t>
+    <t>1511: reference from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - VISIT (70.02-50 &gt; 70.03-27)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.VisitIEN</t>
@@ -1209,7 +1209,7 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
-    <t>1513: reference from REGISTRED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PRIMARY INTERPRETING STAFF (70.02-50 &gt; 70.03-15)</t>
+    <t>1513: reference from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PRIMARY INTERPRETING STAFF (70.02-50 &gt; 70.03-15)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.PrimaryInterpretingStaffIEN</t>
@@ -1911,7 +1911,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="185.78125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="186.9375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="142.56640625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -980,7 +980,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -980,7 +980,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFRadiologyProcedureStatus</t>
+    <t>http://va.gov/fhir/ValueSet/RadiologyProcedureStatus</t>
   </si>
   <si>
     <t xml:space="preserve">us-core-7

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="499">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -999,9 +999,6 @@
     <t>Patient.RadiologyPatient.PatientIEN,Rad.RadiologyExam.PatientIEN,Rad.RadiologyExamActivityLog.PatientIEN,Rad.RadiologyExamContrastMedia.PatientIEN,Rad.RadiologyExamCPTModifier.PatientIEN,Rad.RadiologyExamMedication.PatientIEN,Rad.RadiologyExamSecondaryDiagnosticCode.PatientIEN,Rad.RadiologyExamStatusList.PatientIEN,Rad.RadiologyFilmRegistry.PatientIEN,Rad.RadiologyRegisteredExam.PatientIEN</t>
   </si>
   <si>
-    <t>radiology.case,radiology.dateTime,radiology.modifier [m]</t>
-  </si>
-  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1096,6 +1093,9 @@
     <t>Rad.RadiologyExam.ExamDateTime,Rad.RadiologyExamActivityLog.ExamDateTime,Rad.RadiologyExamContrastMedia.ExamDateTime,Rad.RadiologyExamCPTModifier.ExamDateTime,Rad.RadiologyExamMedication.ExamDateTime,Rad.RadiologyExamSecondaryDiagnosticCode.ExamDateTime,Rad.RadiologyExamStatusList.ExamDateTime,Rad.RadiologyExamTechnologist.ExamDateTime,Rad.RadiologyRegisteredExam.ExamDateTime</t>
   </si>
   <si>
+    <t>RadOrder.Result.FromTime</t>
+  </si>
+  <si>
     <t>Procedure.recorder</t>
   </si>
   <si>
@@ -1273,6 +1273,9 @@
   <si>
     <t>Rad.RadiologyRegisteredExam.RadiologyLocationIEN
 Dim.RadiologyLocation.LocationIEN</t>
+  </si>
+  <si>
+    <t>RadOrder.Result.EnteredAt,RadOrder.Result.PerformedAt</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[classCode=SDLOC]</t>
@@ -1919,7 +1922,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="186.9375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="53.921875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="53.8046875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6716,27 +6719,27 @@
         <v>315</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6759,16 +6762,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6818,7 +6821,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6833,33 +6836,33 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6882,16 +6885,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6929,7 +6932,7 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -6939,7 +6942,7 @@
         <v>215</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6963,27 +6966,27 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>341</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>80</v>
@@ -7005,16 +7008,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7064,7 +7067,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7079,25 +7082,25 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AN42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>341</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -8309,16 +8312,16 @@
         <v>403</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>80</v>
+        <v>404</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>80</v>
@@ -8326,10 +8329,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8355,13 +8358,13 @@
         <v>196</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8390,10 +8393,10 @@
         <v>200</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8411,7 +8414,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8435,13 +8438,13 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>80</v>
@@ -8449,10 +8452,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8475,16 +8478,16 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8534,7 +8537,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8558,13 +8561,13 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>80</v>
@@ -8572,10 +8575,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8601,13 +8604,13 @@
         <v>196</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8636,10 +8639,10 @@
         <v>200</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8657,7 +8660,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8684,21 +8687,21 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8724,13 +8727,13 @@
         <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8759,10 +8762,10 @@
         <v>200</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8780,7 +8783,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8807,7 +8810,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8818,10 +8821,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8844,16 +8847,16 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8903,7 +8906,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8930,7 +8933,7 @@
         <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8941,10 +8944,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8970,13 +8973,13 @@
         <v>196</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9005,10 +9008,10 @@
         <v>200</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -9026,7 +9029,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9053,7 +9056,7 @@
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9064,10 +9067,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9090,17 +9093,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9149,7 +9152,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9176,7 +9179,7 @@
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9187,10 +9190,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9216,10 +9219,10 @@
         <v>196</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9249,10 +9252,10 @@
         <v>200</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -9270,7 +9273,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9297,7 +9300,7 @@
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9308,10 +9311,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9334,13 +9337,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9391,7 +9394,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9415,24 +9418,24 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9458,10 +9461,10 @@
         <v>359</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9512,7 +9515,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9539,7 +9542,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9550,10 +9553,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9671,10 +9674,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9794,10 +9797,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9919,10 +9922,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9948,10 +9951,10 @@
         <v>196</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9981,10 +9984,10 @@
         <v>114</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>80</v>
@@ -10002,7 +10005,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10029,7 +10032,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10040,10 +10043,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10066,13 +10069,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10123,7 +10126,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>90</v>
@@ -10150,7 +10153,7 @@
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10161,10 +10164,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10187,19 +10190,19 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10248,7 +10251,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10275,7 +10278,7 @@
         <v>80</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10286,10 +10289,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10315,13 +10318,13 @@
         <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10350,10 +10353,10 @@
         <v>200</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10371,7 +10374,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10398,7 +10401,7 @@
         <v>80</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file REGISTERED EXAMS (70.02) to us-core-procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file REGISTERED EXAMS (70.02) to us-core-procedure.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="500">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -991,6 +991,10 @@
   </si>
   <si>
     <t>The person, animal or group on which the procedure was performed.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+pr-18-1510:70-.01: if 70-2 &gt; 70.02 then null {null}</t>
   </si>
   <si>
     <t>1510: reference from RAD/NUC MED PATIENT - NAME (70-.01) case 70-2 &gt; 70.02</t>
@@ -6710,36 +6714,36 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>314</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6762,16 +6766,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6821,7 +6825,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6836,33 +6840,33 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6885,16 +6889,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6932,7 +6936,7 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -6942,7 +6946,7 @@
         <v>215</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6966,27 +6970,27 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>80</v>
@@ -7008,16 +7012,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7067,7 +7071,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7082,33 +7086,33 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7131,13 +7135,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7188,7 +7192,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7215,10 +7219,10 @@
         <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>80</v>
@@ -7226,10 +7230,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7252,13 +7256,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7309,7 +7313,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7336,10 +7340,10 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>80</v>
@@ -7347,10 +7351,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7373,13 +7377,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7430,7 +7434,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7454,10 +7458,10 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7468,10 +7472,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7589,10 +7593,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7712,14 +7716,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7741,10 +7745,10 @@
         <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>139</v>
@@ -7799,7 +7803,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7837,10 +7841,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7866,14 +7870,14 @@
         <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7901,10 +7905,10 @@
         <v>200</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7922,7 +7926,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7946,24 +7950,24 @@
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7986,17 +7990,17 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8045,7 +8049,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>90</v>
@@ -8060,33 +8064,33 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8109,17 +8113,17 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8168,7 +8172,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8195,7 +8199,7 @@
         <v>80</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8206,10 +8210,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8232,17 +8236,17 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8291,7 +8295,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8306,22 +8310,22 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>80</v>
@@ -8329,10 +8333,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8358,13 +8362,13 @@
         <v>196</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8393,10 +8397,10 @@
         <v>200</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8414,7 +8418,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8438,13 +8442,13 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>80</v>
@@ -8452,10 +8456,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8478,16 +8482,16 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8537,7 +8541,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8561,13 +8565,13 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>80</v>
@@ -8575,10 +8579,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8604,13 +8608,13 @@
         <v>196</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8639,10 +8643,10 @@
         <v>200</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8660,7 +8664,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8687,21 +8691,21 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8727,13 +8731,13 @@
         <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8762,10 +8766,10 @@
         <v>200</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8783,7 +8787,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8810,7 +8814,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8821,10 +8825,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8847,16 +8851,16 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8906,7 +8910,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8933,7 +8937,7 @@
         <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8944,10 +8948,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8973,13 +8977,13 @@
         <v>196</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9008,10 +9012,10 @@
         <v>200</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -9029,7 +9033,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9056,7 +9060,7 @@
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9067,10 +9071,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9093,17 +9097,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9152,7 +9156,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9179,7 +9183,7 @@
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9190,10 +9194,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9219,10 +9223,10 @@
         <v>196</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9252,10 +9256,10 @@
         <v>200</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -9273,7 +9277,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9300,7 +9304,7 @@
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9311,10 +9315,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9337,13 +9341,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9394,7 +9398,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9418,24 +9422,24 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9458,13 +9462,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9515,7 +9519,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9542,7 +9546,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9553,10 +9557,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9674,10 +9678,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9797,14 +9801,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9826,10 +9830,10 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>139</v>
@@ -9884,7 +9888,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9922,10 +9926,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9951,10 +9955,10 @@
         <v>196</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9984,10 +9988,10 @@
         <v>114</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>80</v>
@@ -10005,7 +10009,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10032,7 +10036,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10043,10 +10047,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10069,13 +10073,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10126,7 +10130,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>90</v>
@@ -10153,7 +10157,7 @@
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10164,10 +10168,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10190,19 +10194,19 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10251,7 +10255,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10278,7 +10282,7 @@
         <v>80</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10289,10 +10293,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10318,13 +10322,13 @@
         <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10353,10 +10357,10 @@
         <v>200</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10374,7 +10378,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10401,7 +10405,7 @@
         <v>80</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -742,7 +742,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1507: source value from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (70.02-50 &gt; 70.03-3.5 &gt; 75.2-.01)</t>
+    <t>1507: source value based on REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (70.02-50 &gt; 70.03-3.5 &gt; 75.2-.01)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -784,7 +784,7 @@
     <t>Procedure.category.text</t>
   </si>
   <si>
-    <t>1508: source value from REGISTERED EXAMS - TYPE OF IMAGING &gt; IMAGING TYPE - TYPE OF IMAGING (70.02-2 &gt; 79.2-.01)</t>
+    <t>1508: source value based on REGISTERED EXAMS - TYPE OF IMAGING &gt; IMAGING TYPE - TYPE OF IMAGING (70.02-2 &gt; 79.2-.01)</t>
   </si>
   <si>
     <t>Rad.RadiologyRegisteredExam.ImagingTypeIEN
@@ -837,7 +837,7 @@
     <t>Procedure.code.coding</t>
   </si>
   <si>
-    <t>1509: source value from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-)</t>
+    <t>1509: source value based on REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-)</t>
   </si>
   <si>
     <t>Procedure.code.coding.id</t>
@@ -912,7 +912,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1509-2: source value from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - CPT CODE (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-.01)</t>
+    <t>1509-2: source value based on REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - CPT CODE (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-.01)</t>
   </si>
   <si>
     <t>./code</t>
@@ -936,7 +936,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1509-3: source value from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - SHORT NAME (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-2)</t>
+    <t>1509-3: source value based on REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PROCEDURE &gt; RAD/NUC MED PROCEDURES - CPT CODE &gt; CPT - SHORT NAME (70.02-50 &gt; 70.03-2 &gt; 71-9 &gt; 81-2)</t>
   </si>
   <si>
     <t>CV.displayName</t>
@@ -994,10 +994,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-pr-18-1510:70-.01: if 70-2 &gt; 70.02 then null {null}</t>
-  </si>
-  <si>
-    <t>1510: reference from RAD/NUC MED PATIENT - NAME (70-.01) case 70-2 &gt; 70.02</t>
+pr-18-1510:If 70-2 &gt; 70.02 then reference null based on (70-.01) {null}</t>
+  </si>
+  <si>
+    <t>1510: reference based on RAD/NUC MED PATIENT - NAME (70-.01) if 70-2 &gt; 70.02</t>
   </si>
   <si>
     <t>Patient.RadiologyPatient.PatientIEN,Rad.RadiologyExam.PatientIEN,Rad.RadiologyExamActivityLog.PatientIEN,Rad.RadiologyExamContrastMedia.PatientIEN,Rad.RadiologyExamCPTModifier.PatientIEN,Rad.RadiologyExamMedication.PatientIEN,Rad.RadiologyExamSecondaryDiagnosticCode.PatientIEN,Rad.RadiologyExamStatusList.PatientIEN,Rad.RadiologyFilmRegistry.PatientIEN,Rad.RadiologyRegisteredExam.PatientIEN</t>
@@ -1031,7 +1031,7 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
   </si>
   <si>
-    <t>1511: reference from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - VISIT (70.02-50 &gt; 70.03-27)</t>
+    <t>1511: reference based on REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - VISIT (70.02-50 &gt; 70.03-27)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.VisitIEN</t>
@@ -1091,7 +1091,7 @@
 </t>
   </si>
   <si>
-    <t>1512: source value from REGISTERED EXAMS - EXAM DATE (70.02-.01)</t>
+    <t>1512: source value based on REGISTERED EXAMS - EXAM DATE (70.02-.01)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.ExamDateTime,Rad.RadiologyExamActivityLog.ExamDateTime,Rad.RadiologyExamContrastMedia.ExamDateTime,Rad.RadiologyExamCPTModifier.ExamDateTime,Rad.RadiologyExamMedication.ExamDateTime,Rad.RadiologyExamSecondaryDiagnosticCode.ExamDateTime,Rad.RadiologyExamStatusList.ExamDateTime,Rad.RadiologyExamTechnologist.ExamDateTime,Rad.RadiologyRegisteredExam.ExamDateTime</t>
@@ -1219,7 +1219,7 @@
     <t>A reference to Device supports use cases, such as pacemakers.</t>
   </si>
   <si>
-    <t>1513: reference from REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PRIMARY INTERPRETING STAFF (70.02-50 &gt; 70.03-15)</t>
+    <t>1513: reference based on REGISTERED EXAMS - EXAMINATIONS &gt; EXAMINATIONS - PRIMARY INTERPRETING STAFF (70.02-50 &gt; 70.03-15)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.PrimaryInterpretingStaffIEN</t>
@@ -1272,7 +1272,7 @@
     <t>Ties a procedure to where the records are likely kept.</t>
   </si>
   <si>
-    <t>1514: reference from REGISTERED EXAMS - IMAGING LOCATION &gt; IMAGING LOCATIONS - LOCATION (70.02-4 &gt; 79.1-.01)</t>
+    <t>1514: reference based on REGISTERED EXAMS - IMAGING LOCATION &gt; IMAGING LOCATIONS - LOCATION (70.02-4 &gt; 79.1-.01)</t>
   </si>
   <si>
     <t>Rad.RadiologyRegisteredExam.RadiologyLocationIEN
@@ -1924,7 +1924,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="186.9375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="189.12109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="53.8046875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2726" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -602,6 +602,9 @@
   </si>
   <si>
     <t>required</t>
+  </si>
+  <si>
+    <t>see mapping [VF_RadiologyProcedureStatus](ConceptMap-VF-RadiologyProcedureStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/RadiologyProcedureStatus</t>
@@ -1913,7 +1916,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.0546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="87.8984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="56.48828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -3849,9 +3852,11 @@
       <c r="X16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3878,13 +3883,13 @@
         <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>80</v>
@@ -3893,13 +3898,13 @@
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>80</v>
@@ -3907,14 +3912,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3933,16 +3938,16 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3968,13 +3973,13 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3992,7 +3997,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4016,10 +4021,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -4030,10 +4035,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4056,13 +4061,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4113,7 +4118,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4140,7 +4145,7 @@
         <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4151,10 +4156,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4183,7 +4188,7 @@
         <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>139</v>
@@ -4224,19 +4229,19 @@
         <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4263,7 +4268,7 @@
         <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -4274,10 +4279,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4300,19 +4305,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4361,7 +4366,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4388,21 +4393,21 @@
         <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4425,19 +4430,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4486,7 +4491,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4501,7 +4506,7 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
@@ -4513,21 +4518,21 @@
         <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4550,13 +4555,13 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4583,13 +4588,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4607,7 +4612,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4634,10 +4639,10 @@
         <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>80</v>
@@ -4645,10 +4650,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4671,13 +4676,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4728,7 +4733,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4755,7 +4760,7 @@
         <v>80</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -4766,10 +4771,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4798,7 +4803,7 @@
         <v>137</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>139</v>
@@ -4839,19 +4844,19 @@
         <v>80</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4878,7 +4883,7 @@
         <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -4889,10 +4894,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4915,19 +4920,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4976,7 +4981,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5003,21 +5008,21 @@
         <v>80</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5040,19 +5045,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5101,7 +5106,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5116,10 +5121,10 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -5128,25 +5133,25 @@
         <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5165,17 +5170,17 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -5200,13 +5205,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5224,7 +5229,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5248,24 +5253,24 @@
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5288,13 +5293,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5345,7 +5350,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5372,7 +5377,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5383,10 +5388,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5415,7 +5420,7 @@
         <v>137</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>139</v>
@@ -5456,19 +5461,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5495,7 +5500,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5506,10 +5511,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5532,19 +5537,19 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5593,7 +5598,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5608,7 +5613,7 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>80</v>
@@ -5620,21 +5625,21 @@
         <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5657,13 +5662,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5714,7 +5719,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5741,7 +5746,7 @@
         <v>80</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5752,10 +5757,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5784,7 +5789,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5825,19 +5830,19 @@
         <v>80</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5864,7 +5869,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5875,10 +5880,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5904,16 +5909,16 @@
         <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5923,7 +5928,7 @@
         <v>80</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>80</v>
@@ -5962,7 +5967,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5977,7 +5982,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5989,21 +5994,21 @@
         <v>80</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6026,16 +6031,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6085,7 +6090,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6112,21 +6117,21 @@
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6152,14 +6157,14 @@
         <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6208,7 +6213,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6223,7 +6228,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
@@ -6235,21 +6240,21 @@
         <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6272,17 +6277,17 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6331,7 +6336,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6346,7 +6351,7 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -6358,21 +6363,21 @@
         <v>80</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6395,19 +6400,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6456,7 +6461,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6483,21 +6488,21 @@
         <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6520,19 +6525,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6581,7 +6586,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6608,25 +6613,25 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6645,13 +6650,13 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6702,7 +6707,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>90</v>
@@ -6714,36 +6719,36 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6766,16 +6771,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6825,7 +6830,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6840,33 +6845,33 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6889,16 +6894,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6936,17 +6941,17 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6955,7 +6960,7 @@
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
@@ -6970,27 +6975,27 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>80</v>
@@ -7012,16 +7017,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7071,7 +7076,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7080,39 +7085,39 @@
         <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7135,13 +7140,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7192,7 +7197,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7219,10 +7224,10 @@
         <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>80</v>
@@ -7230,10 +7235,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7256,13 +7261,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7313,7 +7318,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7340,10 +7345,10 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>80</v>
@@ -7351,10 +7356,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7377,13 +7382,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7434,7 +7439,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7458,10 +7463,10 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7472,10 +7477,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7498,13 +7503,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7555,7 +7560,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7582,7 +7587,7 @@
         <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7593,10 +7598,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7625,7 +7630,7 @@
         <v>137</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7678,7 +7683,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7705,7 +7710,7 @@
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7716,14 +7721,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7745,10 +7750,10 @@
         <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>139</v>
@@ -7803,7 +7808,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7841,10 +7846,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7867,17 +7872,17 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7902,13 +7907,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7926,7 +7931,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7950,24 +7955,24 @@
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7990,17 +7995,17 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8049,7 +8054,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>90</v>
@@ -8064,33 +8069,33 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8113,17 +8118,17 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8172,7 +8177,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8199,7 +8204,7 @@
         <v>80</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8210,10 +8215,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8236,17 +8241,17 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8295,7 +8300,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8310,22 +8315,22 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>80</v>
@@ -8333,10 +8338,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8359,16 +8364,16 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8394,13 +8399,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8418,7 +8423,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8442,13 +8447,13 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>80</v>
@@ -8456,10 +8461,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8482,16 +8487,16 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8541,7 +8546,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8565,13 +8570,13 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>80</v>
@@ -8579,10 +8584,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8605,16 +8610,16 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8640,13 +8645,13 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8664,7 +8669,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8691,21 +8696,21 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8728,16 +8733,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8763,13 +8768,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8787,7 +8792,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8814,7 +8819,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8825,10 +8830,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8851,16 +8856,16 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8910,7 +8915,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8937,7 +8942,7 @@
         <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8948,10 +8953,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8974,16 +8979,16 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9009,13 +9014,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -9033,7 +9038,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9060,7 +9065,7 @@
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9071,10 +9076,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9097,17 +9102,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9156,7 +9161,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9183,7 +9188,7 @@
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9194,10 +9199,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9220,13 +9225,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9253,13 +9258,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -9277,7 +9282,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9304,7 +9309,7 @@
         <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9315,10 +9320,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9341,13 +9346,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9398,7 +9403,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9422,24 +9427,24 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9462,13 +9467,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9519,7 +9524,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9546,7 +9551,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9557,10 +9562,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9583,13 +9588,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9640,7 +9645,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9667,7 +9672,7 @@
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9678,10 +9683,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9710,7 +9715,7 @@
         <v>137</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>139</v>
@@ -9763,7 +9768,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9790,7 +9795,7 @@
         <v>80</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9801,14 +9806,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9830,10 +9835,10 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>139</v>
@@ -9888,7 +9893,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9926,10 +9931,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9952,13 +9957,13 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9988,10 +9993,10 @@
         <v>114</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>80</v>
@@ -10009,7 +10014,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10036,7 +10041,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -10047,10 +10052,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10073,13 +10078,13 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10130,7 +10135,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>90</v>
@@ -10157,7 +10162,7 @@
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10168,10 +10173,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10194,19 +10199,19 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10255,7 +10260,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10282,7 +10287,7 @@
         <v>80</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10293,10 +10298,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10319,16 +10324,16 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10354,13 +10359,13 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10378,7 +10383,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10405,7 +10410,7 @@
         <v>80</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -997,7 +997,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-pr-18-1510:If 70-2 &gt; 70.02 then reference null based on (70-.01) {null}</t>
+pr-18-1510:If 70-2 &gt; 70.02 then reference null based on (70-.01) {true}</t>
   </si>
   <si>
     <t>1510: reference based on RAD/NUC MED PATIENT - NAME (70-.01) if 70-2 &gt; 70.02</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -986,7 +986,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -997,7 +997,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-pr-18-1510:If 70-2 &gt; 70.02 then reference null based on (70-.01) {true}</t>
+pr-18-1510:If 70-2 &gt; 70.02 then reference /Patient based on (70-.01) {true}</t>
   </si>
   <si>
     <t>1510: reference based on RAD/NUC MED PATIENT - NAME (70-.01) if 70-2 &gt; 70.02</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiology.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
